--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/da-metrics-medium.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/da-metrics-medium.xlsx
@@ -463,10 +463,10 @@
         <v>Tỷ lệ $LTV : CAC \ge 3 : 1$ — giá trị vòng đời lớn hơn gấp 3 lần chi phí thu hút</v>
       </c>
       <c r="G2" t="str">
+        <v>Tỷ lệ $LTV : CAC &lt; 1 : 2$ — chi phí thu hút khách hàng lớn gấp đôi giá trị vòng đời</v>
+      </c>
+      <c r="H2" t="str">
         <v>Tỷ lệ $LTV : CAC = 1 : 1$ — doanh thu vòng đời bằng đúng chi phí bỏ ra thu hút</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Tỷ lệ $LTV : CAC &lt; 1 : 2$ — chi phí thu hút khách hàng lớn gấp đôi giá trị vòng đời</v>
       </c>
       <c r="I2" t="str">
         <v>Hai chỉ số này hoàn toàn độc lập và không có mối quan hệ tài chính nào với nhau — độc lập chỉ số</v>
@@ -492,10 +492,10 @@
         <v>ARPU (Average Revenue Per User) giúp đánh giá hiệu quả kinh doanh của sản phẩm. ARPU tăng chứng tỏ doanh nghiệp đang thực hiện tốt việc bán thêm (upsell) hoặc tăng giá trị dịch vụ cung cấp cho tập khách hàng hiện có.</v>
       </c>
       <c r="F3" t="str">
+        <v>Tổng số lượng đơn hàng chia cho tổng số lượng khách hàng đăng ký tài khoản; phản ánh tần suất mua sắm — tần suất mua hàng</v>
+      </c>
+      <c r="G3" t="str">
         <v>Tổng doanh thu chia cho tổng số lượng người dùng hoạt động (Active Users) trong một khoảng thời gian; phản ánh khả năng kiếm tiền (Monetization) trên mỗi người dùng — doanh thu trung bình trên mỗi người dùng</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Tổng số lượng đơn hàng chia cho tổng số lượng khách hàng đăng ký tài khoản; phản ánh tần suất mua sắm — tần suất mua hàng</v>
       </c>
       <c r="H3" t="str">
         <v>Tổng chi phí phát triển phần mềm chia cho tổng số lượng người dùng; phản ánh giá thành công nghệ — chi phí công nghệ bình quân</v>
@@ -504,7 +504,7 @@
         <v>Tổng số lượng đánh giá tốt chia cho tổng số lượng người dùng hoạt động; phản ánh mức độ yêu thích sản phẩm — mức độ yêu thích</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -527,13 +527,13 @@
         <v>DAU/MAU đo lường mức độ kết dính (Stickiness - tần suất người dùng quay lại hàng ngày trong tháng); Retention Rate đo lường tỷ lệ người dùng còn hoạt động sau một khoảng thời gian kể từ ngày đầu tiên sử dụng — kết dính vs giữ chân</v>
       </c>
       <c r="G4" t="str">
-        <v>DAU/MAU chỉ áp dụng cho trang web; còn Retention Rate chỉ sử dụng cho ứng dụng di động — phân loại nền tảng</v>
+        <v>DAU/MAU do phòng IT quản trị; còn Retention Rate do phòng nhân sự quản lý báo cáo — phòng ban quản lý</v>
       </c>
       <c r="H4" t="str">
         <v>DAU/MAU đo lường doanh thu tài chính; còn Retention Rate đo lường chi phí marketing — doanh thu vs chi phí</v>
       </c>
       <c r="I4" t="str">
-        <v>DAU/MAU do phòng IT quản trị; còn Retention Rate do phòng nhân sự quản lý báo cáo — phòng ban quản lý</v>
+        <v>DAU/MAU chỉ áp dụng cho trang web; còn Retention Rate chỉ sử dụng cho ứng dụng di động — phân loại nền tảng</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -556,19 +556,19 @@
         <v>Payback Period quyết định tính sống còn của dòng tiền. Ví dụ, nếu CAC = 120 USD, ARPU hàng tháng = 10 USD, thì mất 12 tháng để hoàn vốn CAC. Nếu khách hàng rời bỏ app (churn) ở tháng thứ 6, doanh nghiệp sẽ lỗ 60 USD trên khách hàng đó. Doanh nghiệp SaaS hướng tới Payback Period dưới 12 tháng.</v>
       </c>
       <c r="F5" t="str">
+        <v>Số năm cần thiết để doanh nghiệp trả hết nợ vay ngân hàng để xây dựng tòa nhà văn phòng — thời gian hoàn nợ vay</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Thời gian trung bình để đội ngũ hỗ trợ giải quyết xong một khiếu nại của khách hàng — thời gian xử lý khiếu nại</v>
+      </c>
+      <c r="H5" t="str">
         <v>Số tháng cần thiết để doanh thu từ một khách hàng bù đắp lại chi phí CAC bỏ ra để có được khách hàng đó; thời gian hoàn vốn càng ngắn giúp dòng tiền quay vòng nhanh và giảm rủi ro tài chính — thời gian hoàn vốn CAC</v>
       </c>
-      <c r="G5" t="str">
-        <v>Số năm cần thiết để doanh nghiệp trả hết nợ vay ngân hàng để xây dựng tòa nhà văn phòng — thời gian hoàn nợ vay</v>
-      </c>
-      <c r="H5" t="str">
+      <c r="I5" t="str">
         <v>Số ngày mà khách hàng được phép nợ tiền thanh toán hóa đơn kể từ khi nhận được hàng — thời hạn thanh toán nợ</v>
       </c>
-      <c r="I5" t="str">
-        <v>Thời gian trung bình để đội ngũ hỗ trợ giải quyết xong một khiếu nại của khách hàng — thời gian xử lý khiếu nại</v>
-      </c>
       <c r="J5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -623,13 +623,13 @@
         <v>Tỷ lệ doanh thu định kỳ giữ chân được từ tập khách hàng cũ sau khi đã cộng thêm doanh thu nâng cấp (Upsell) và trừ đi doanh thu mất mát do rời bỏ (Churn) — sức khỏe doanh thu từ khách hàng cũ</v>
       </c>
       <c r="G7" t="str">
-        <v>Tổng doanh thu thuần thu được từ các chiến dịch quảng cáo trực tuyến trực tiếp — doanh thu chiến dịch quảng cáo</v>
+        <v>Số lượng khách hàng đăng ký mới thông qua sự giới thiệu của khách hàng cũ — số lượng khách giới thiệu</v>
       </c>
       <c r="H7" t="str">
         <v>Tỷ lệ phần trăm lợi nhuận biên sau khi đã trừ đi toàn bộ chi phí sản xuất phần mềm — tỷ suất lợi nhuận biên</v>
       </c>
       <c r="I7" t="str">
-        <v>Số lượng khách hàng đăng ký mới thông qua sự giới thiệu của khách hàng cũ — số lượng khách giới thiệu</v>
+        <v>Tổng doanh thu thuần thu được từ các chiến dịch quảng cáo trực tuyến trực tiếp — doanh thu chiến dịch quảng cáo</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -652,19 +652,19 @@
         <v>Customer Lifetime = $1 / \text{Churn Rate}$. Với Churn Rate hàng tháng = 5% (0.05), Lifetime trung bình của khách hàng là $1 / 0.05 = 20$ tháng.</v>
       </c>
       <c r="F8" t="str">
+        <v>Không thể tính toán được nếu không có số lượng khách hàng cụ thể đầu kỳ — thiếu dữ liệu</v>
+      </c>
+      <c r="G8" t="str">
         <v>20 tháng — tính bằng công thức $1 / Churn\_Rate$ — thời gian gắn bó trung bình</v>
       </c>
-      <c r="G8" t="str">
+      <c r="H8" t="str">
         <v>5 tháng — dựa trên tỷ lệ phần trăm chênh lệch — thời gian gắn bó ngắn</v>
       </c>
-      <c r="H8" t="str">
+      <c r="I8" t="str">
         <v>50 tháng — tính theo quy mô lũy kế năm tài chính — thời gian gắn bó dài</v>
       </c>
-      <c r="I8" t="str">
-        <v>Không thể tính toán được nếu không có số lượng khách hàng cụ thể đầu kỳ — thiếu dữ liệu</v>
-      </c>
       <c r="J8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -684,19 +684,19 @@
         <v>ARR chỉ tính phần doanh thu có tính lặp lại (subscriptions). Run Rate (nhân doanh thu tháng gần nhất với 12) bao gồm cả doanh thu một lần (one-off sales, consulting fees), mang tính chất dự đoán giả định tương lai có thể không phản ánh đúng thực tế nếu có tính mùa vụ.</v>
       </c>
       <c r="F9" t="str">
+        <v>ARR chỉ dùng cho doanh nghiệp phần cứng; còn Run Rate chỉ dùng cho doanh nghiệp phần mềm — phân loại doanh nghiệp</v>
+      </c>
+      <c r="G9" t="str">
         <v>ARR là doanh thu định kỳ năm từ các hợp đồng subscription hoạt động; Run Rate là doanh thu dự phóng cả năm dựa trên kết quả doanh thu của một tháng/quý gần nhất nhân lên — doanh thu định kỳ thực tế vs doanh thu dự phóng</v>
       </c>
-      <c r="G9" t="str">
-        <v>ARR chỉ dùng cho doanh nghiệp phần cứng; còn Run Rate chỉ dùng cho doanh nghiệp phần mềm — phân loại doanh nghiệp</v>
-      </c>
       <c r="H9" t="str">
+        <v>ARR luôn luôn có giá trị lớn gấp 12 lần so với Run Rate Revenue — so sánh quy mô chỉ số</v>
+      </c>
+      <c r="I9" t="str">
         <v>ARR bắt buộc phải được kiểm toán bởi chính phủ; còn Run Rate do doanh nghiệp tự công bố nội bộ — tính pháp lý</v>
       </c>
-      <c r="I9" t="str">
-        <v>ARR luôn luôn có giá trị lớn gấp 12 lần so với Run Rate Revenue — so sánh quy mô chỉ số</v>
-      </c>
       <c r="J9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -716,19 +716,19 @@
         <v>NPS được tính bằng %Promoters - %Detractors. Trường hợp tệ nhất là 100% người dùng là Detractors (NPS = -100). Trường hợp tốt nhất là 100% người dùng là Promoters (NPS = +100). NPS trên 50 được coi là xuất sắc.</v>
       </c>
       <c r="F10" t="str">
+        <v>Từ 0% đến 100% — tỷ lệ phần trăm phân bổ khách hàng ủng hộ</v>
+      </c>
+      <c r="G10" t="str">
         <v>Từ -100 đến +100 — thang điểm đánh giá lòng trung thành</v>
       </c>
-      <c r="G10" t="str">
+      <c r="H10" t="str">
         <v>Từ 0 đến 10 — thang điểm đánh giá mức độ hài lòng đơn giản</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Từ 0% đến 100% — tỷ lệ phần trăm phân bổ khách hàng ủng hộ</v>
       </c>
       <c r="I10" t="str">
         <v>Từ -1 đến +1 — hệ số tương quan tuyến tính của lòng trung thành</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -748,19 +748,19 @@
         <v>ROAS đo lường hiệu quả trực tiếp của chi tiêu quảng cáo (ví dụ: ROAS = 4x hoặc 400% nghĩa là bỏ ra 1 USD chạy ads thu về 4 USD doanh thu). Khác với ROI vì ROAS chỉ tính chi phí ads trực tiếp, chưa tính các chi phí vận hành khác.</v>
       </c>
       <c r="F11" t="str">
+        <v>Tổng số lượng click chuột vào quảng cáo chia cho tổng số lượt hiển thị quảng cáo — tỷ lệ click CTR</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Tổng chi phí quảng cáo chia cho số lượng khách hàng thực hiện đăng ký tài khoản — chi phí mỗi lượt đăng ký</v>
+      </c>
+      <c r="H11" t="str">
         <v>Doanh thu thu được từ chiến dịch quảng cáo chia cho tổng chi phí chạy quảng cáo đó — hiệu quả chi tiêu quảng cáo</v>
-      </c>
-      <c r="G11" t="str">
-        <v>Tổng số lượng click chuột vào quảng cáo chia cho tổng số lượt hiển thị quảng cáo — tỷ lệ click CTR</v>
-      </c>
-      <c r="H11" t="str">
-        <v>Tổng chi phí quảng cáo chia cho số lượng khách hàng thực hiện đăng ký tài khoản — chi phí mỗi lượt đăng ký</v>
       </c>
       <c r="I11" t="str">
         <v>Tổng số lượng đơn hàng thành công chia cho số lượng click chuột vào quảng cáo — tỷ lệ chuyển đổi click</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
